--- a/MATH/M04/bus123-math-m04-l01-starter.xlsx
+++ b/MATH/M04/bus123-math-m04-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R190916d5a17d43a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R44a29987f8c143d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rb08c25afeb2f43cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Ra1fa30031cce4367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rc7cf5238ee2c472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rfb555b6cbac84ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rfd63eceeab1346a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R1e7f5eec196c4bf9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,14 +16,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="$#,##0"/>
     <x:numFmt numFmtId="166" formatCode="0.0%"/>
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="23">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -152,8 +153,14 @@
       <x:color rgb="FF0E1116"/>
       <x:name val="DM Sans"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -318,6 +325,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -395,7 +417,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="209">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -931,6 +953,38 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="21" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="23" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="23" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1257,10 +1311,8 @@
       <x:c r="F2" s="46" t="n"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Live You Try It is self-graded with hints and feedback. Class Challenge is the graded or next-level activity.</x:t>
-        </x:is>
+      <x:c r="A3" s="48" t="str">
+        <x:v>Build and label your own live models, then compare with the slide reveals.</x:v>
       </x:c>
       <x:c r="B3" s="46" t="n"/>
       <x:c r="C3" s="46" t="n"/>
@@ -1300,69 +1352,59 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
+    <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What to do first</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open the Live You Try It tab during the slide pauses. Use the exact numbers from the worked examples.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="8" t="n"/>
-      <x:c r="D5" s="8" t="n"/>
-      <x:c r="E5" s="8" t="n"/>
-      <x:c r="F5" s="8" t="n"/>
-    </x:row>
-    <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-grade live practice</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the hint and feedback cells to check your formula logic before moving on.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="8" t="n"/>
-      <x:c r="D6" s="8" t="n"/>
-      <x:c r="E6" s="8" t="n"/>
-      <x:c r="F6" s="8" t="n"/>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="B5" s="209" t="str">
+        <x:v>Open Live You Try It during the slide pauses. Read each new scenario and choose your own model layout.</x:v>
+      </x:c>
+      <x:c r="C5" s="210" t="n"/>
+      <x:c r="D5" s="210" t="n"/>
+      <x:c r="E5" s="210" t="n"/>
+      <x:c r="F5" s="210" t="n"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>Build your model</x:v>
+      </x:c>
+      <x:c r="B6" s="209" t="str">
+        <x:v>Write labels, enter inputs, and calculate with cell references. Format money, percentages, and whole guests.</x:v>
+      </x:c>
+      <x:c r="C6" s="210" t="n"/>
+      <x:c r="D6" s="210" t="n"/>
+      <x:c r="E6" s="210" t="n"/>
+      <x:c r="F6" s="210" t="n"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Then level up</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the Class Challenge tab for harder scenarios that combine markup, markdown, and break-even.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="8" t="n"/>
-      <x:c r="D7" s="8" t="n"/>
-      <x:c r="E7" s="8" t="n"/>
-      <x:c r="F7" s="8" t="n"/>
-    </x:row>
-    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="B7" s="209" t="str">
+        <x:v>After live practice, use Class Challenge for scenarios that combine pricing and break-even.</x:v>
+      </x:c>
+      <x:c r="C7" s="210" t="n"/>
+      <x:c r="D7" s="210" t="n"/>
+      <x:c r="E7" s="210" t="n"/>
+      <x:c r="F7" s="210" t="n"/>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Remember</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name the base first: cost, original selling price, or contribution margin.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="8" t="n"/>
-      <x:c r="D8" s="8" t="n"/>
-      <x:c r="E8" s="8" t="n"/>
-      <x:c r="F8" s="8" t="n"/>
+      <x:c r="B8" s="209" t="str">
+        <x:v>Compare logic and answers with the slide reveal. Different cell locations are valid.</x:v>
+      </x:c>
+      <x:c r="C8" s="210" t="n"/>
+      <x:c r="D8" s="210" t="n"/>
+      <x:c r="E8" s="210" t="n"/>
+      <x:c r="F8" s="210" t="n"/>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="9" t="inlineStr">
@@ -1462,335 +1504,411 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Live You Try It</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="175" t="n"/>
-      <x:c r="C1" s="175" t="n"/>
-      <x:c r="D1" s="175" t="n"/>
-      <x:c r="E1" s="175" t="n"/>
-      <x:c r="F1" s="175" t="n"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="47" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-graded practice using the exact numbers from the slides</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="46" t="n"/>
-      <x:c r="C2" s="46" t="n"/>
-      <x:c r="D2" s="46" t="n"/>
-      <x:c r="E2" s="46" t="n"/>
-      <x:c r="F2" s="46" t="n"/>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter yellow inputs, build blue formulas, then read the green feedback. These cells are for learning, not private grading.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="46" t="n"/>
-      <x:c r="C3" s="46" t="n"/>
-      <x:c r="D3" s="46" t="n"/>
-      <x:c r="E3" s="46" t="n"/>
-      <x:c r="F3" s="46" t="n"/>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="215" t="str">
+        <x:v>Live You Try It</x:v>
+      </x:c>
+      <x:c r="B1" s="215"/>
+      <x:c r="C1" s="215"/>
+      <x:c r="D1" s="215"/>
+      <x:c r="E1" s="215"/>
+      <x:c r="F1" s="215"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="216" t="str">
+        <x:v>Choose your own cells. Label inputs, enter values, and build formulas using cell references.</x:v>
+      </x:c>
+      <x:c r="B2" s="216"/>
+      <x:c r="C2" s="216"/>
+      <x:c r="D2" s="216"/>
+      <x:c r="E2" s="216"/>
+      <x:c r="F2" s="216"/>
+    </x:row>
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="216" t="str">
+        <x:v>Explain your result, then compare with the slide reveal. Use the blank space below each scenario.</x:v>
+      </x:c>
+      <x:c r="B3" s="216"/>
+      <x:c r="C3" s="216"/>
+      <x:c r="D3" s="216"/>
+      <x:c r="E3" s="216"/>
+      <x:c r="F3" s="216"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="184" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pause</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="184" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What to model</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="184" t="str">
-        <x:v>Given input</x:v>
-      </x:c>
-      <x:c r="D4" s="184" t="str">
-        <x:v>Your formula / result</x:v>
-      </x:c>
-      <x:c r="E4" s="184" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="184" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="52" customHeight="1">
-      <x:c r="A5" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="185" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="177" t="n"/>
-      <x:c r="E5" s="84" t="str">
-        <x:v>Use the tasting box cost from the worked example.</x:v>
-      </x:c>
-      <x:c r="F5" s="84" t="n"/>
-    </x:row>
-    <x:row r="6" ht="52" customHeight="1">
-      <x:c r="A6" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup rate from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="186" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="D6" s="177" t="n"/>
-      <x:c r="E6" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter 45% as a percent.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="84" t="n"/>
-    </x:row>
-    <x:row r="7" ht="52" customHeight="1">
-      <x:c r="A7" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Selling price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="177" t="n"/>
-      <x:c r="D7" s="187"/>
-      <x:c r="E7" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost x (1 + Markup Rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="88" t="str">
-        <x:f>IF(ABS(D7-26.1)&lt;0.01,"Correct: markup builds from $18.00 to $26.10.","Check the base: use cost, then multiply by 1 + markup rate.")</x:f>
-        <x:v>Check the base: use cost, then multiply by 1 + markup rate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="52" customHeight="1">
-      <x:c r="A8" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Original price from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="185" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D8" s="177" t="n"/>
-      <x:c r="E8" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the original selling price before the discount.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="84" t="n"/>
-    </x:row>
-    <x:row r="9" ht="52" customHeight="1">
-      <x:c r="A9" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown rate from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="186" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="D9" s="177" t="n"/>
-      <x:c r="E9" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter 20% as a percent.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="84" t="n"/>
-    </x:row>
-    <x:row r="10" ht="52" customHeight="1">
-      <x:c r="A10" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sale price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="180" t="n"/>
-      <x:c r="D10" s="187"/>
-      <x:c r="E10" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Original Price x (1 - Markdown Rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="84" t="str">
-        <x:f>IF(ABS(D10-41.6)&lt;0.01,"Correct: the markdown price is $41.60.","Check the base: markdown starts from original price, not cost.")</x:f>
-        <x:v>Check the base: markdown starts from original price, not cost.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="52" customHeight="1">
-      <x:c r="A11" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fixed costs from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="185" t="n">
-        <x:v>3600</x:v>
-      </x:c>
-      <x:c r="D11" s="181" t="n"/>
-      <x:c r="E11" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fixed costs stay the same across guests.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="88" t="n"/>
-    </x:row>
-    <x:row r="12" ht="52" customHeight="1">
-      <x:c r="A12" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Selling price from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="185" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D12" s="177" t="n"/>
-      <x:c r="E12" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ticket price per guest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="84" t="n"/>
-    </x:row>
-    <x:row r="13" ht="52" customHeight="1">
-      <x:c r="A13" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Variable cost from slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="185" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D13" s="177" t="n"/>
-      <x:c r="E13" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost that moves with each guest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="84" t="n"/>
-    </x:row>
-    <x:row r="14" ht="52" customHeight="1">
-      <x:c r="A14" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contribution margin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="182" t="n"/>
-      <x:c r="D14" s="187"/>
-      <x:c r="E14" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Selling price - variable cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="84" t="str">
-        <x:f>IF(ABS(D14-21)&lt;0.01,"Correct: each guest contributes $21 before fixed costs.","Calculate contribution margin before break-even.")</x:f>
-        <x:v>Calculate contribution margin before break-even.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="52" customHeight="1">
-      <x:c r="A15" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even guests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="182" t="n"/>
-      <x:c r="D15" s="188"/>
-      <x:c r="E15" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fixed costs ÷ contribution margin; round up.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="84" t="str">
-        <x:f>IF(D15=172,"Correct: Anchor &amp; Oak needs 172 guests to break even.","Round up because the event cannot sell part of a guest.")</x:f>
-        <x:v>Round up because the event cannot sell part of a guest.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="D16"/>
-      <x:c r="F16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="D17"/>
-      <x:c r="F17"/>
+      <x:c r="A4" s="218" t="str">
+        <x:v>Markup — Set the catering-package price</x:v>
+      </x:c>
+      <x:c r="B4" s="218"/>
+      <x:c r="C4" s="218"/>
+      <x:c r="D4" s="218"/>
+      <x:c r="E4" s="218"/>
+      <x:c r="F4" s="218"/>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="220" t="str">
+        <x:v>Anchor &amp; Oak is pricing a boxed catering package. Each package costs $24, and the company wants a 35% markup on cost. What selling price should it charge?</x:v>
+      </x:c>
+      <x:c r="B5" s="220"/>
+      <x:c r="C5" s="220"/>
+      <x:c r="D5" s="220"/>
+      <x:c r="E5" s="220"/>
+      <x:c r="F5" s="220"/>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="220"/>
+      <x:c r="B6" s="220"/>
+      <x:c r="C6" s="220"/>
+      <x:c r="D6" s="220"/>
+      <x:c r="E6" s="220"/>
+      <x:c r="F6" s="220"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="213"/>
+      <x:c r="B7" s="213"/>
+      <x:c r="C7" s="213"/>
+      <x:c r="D7" s="213"/>
+      <x:c r="E7" s="213"/>
+      <x:c r="F7" s="213"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="213"/>
+      <x:c r="B8" s="213"/>
+      <x:c r="C8" s="213"/>
+      <x:c r="D8" s="213"/>
+      <x:c r="E8" s="213"/>
+      <x:c r="F8" s="213"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="213"/>
+      <x:c r="B9" s="213"/>
+      <x:c r="C9" s="213"/>
+      <x:c r="D9" s="213"/>
+      <x:c r="E9" s="213"/>
+      <x:c r="F9" s="213"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="213"/>
+      <x:c r="B10" s="213"/>
+      <x:c r="C10" s="213"/>
+      <x:c r="D10" s="213"/>
+      <x:c r="E10" s="213"/>
+      <x:c r="F10" s="213"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="213"/>
+      <x:c r="B11" s="213"/>
+      <x:c r="C11" s="213"/>
+      <x:c r="D11" s="213"/>
+      <x:c r="E11" s="213"/>
+      <x:c r="F11" s="213"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="213"/>
+      <x:c r="B12" s="213"/>
+      <x:c r="C12" s="213"/>
+      <x:c r="D12" s="213"/>
+      <x:c r="E12" s="213"/>
+      <x:c r="F12" s="213"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="213"/>
+      <x:c r="B13" s="213"/>
+      <x:c r="C13" s="213"/>
+      <x:c r="D13" s="213"/>
+      <x:c r="E13" s="213"/>
+      <x:c r="F13" s="213"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="213"/>
+      <x:c r="B14" s="213"/>
+      <x:c r="C14" s="213"/>
+      <x:c r="D14" s="213"/>
+      <x:c r="E14" s="213"/>
+      <x:c r="F14" s="213"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="213"/>
+      <x:c r="B15" s="213"/>
+      <x:c r="C15" s="213"/>
+      <x:c r="D15" s="213"/>
+      <x:c r="E15" s="213"/>
+      <x:c r="F15" s="213"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="213"/>
+      <x:c r="B16" s="213"/>
+      <x:c r="C16" s="213"/>
+      <x:c r="D16" s="213"/>
+      <x:c r="E16" s="213"/>
+      <x:c r="F16" s="213"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="213"/>
+      <x:c r="B17" s="213"/>
+      <x:c r="C17" s="213"/>
+      <x:c r="D17" s="213"/>
+      <x:c r="E17" s="213"/>
+      <x:c r="F17" s="213"/>
+    </x:row>
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="218" t="str">
+        <x:v>Markdown — Price the late-ticket promotion</x:v>
+      </x:c>
+      <x:c r="B18" s="218"/>
+      <x:c r="C18" s="218"/>
+      <x:c r="D18" s="218"/>
+      <x:c r="E18" s="218"/>
+      <x:c r="F18" s="218"/>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="220" t="str">
+        <x:v>Anchor &amp; Oak has unsold seats for a tasting event. The original ticket price is $64, and the company offers a 25% markdown. What is the promotional ticket price?</x:v>
+      </x:c>
+      <x:c r="B19" s="220"/>
+      <x:c r="C19" s="220"/>
+      <x:c r="D19" s="220"/>
+      <x:c r="E19" s="220"/>
+      <x:c r="F19" s="220"/>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="220"/>
+      <x:c r="B20" s="220"/>
+      <x:c r="C20" s="220"/>
+      <x:c r="D20" s="220"/>
+      <x:c r="E20" s="220"/>
+      <x:c r="F20" s="220"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="213"/>
+      <x:c r="B21" s="213"/>
+      <x:c r="C21" s="213"/>
+      <x:c r="D21" s="213"/>
+      <x:c r="E21" s="213"/>
+      <x:c r="F21" s="213"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="213"/>
+      <x:c r="B22" s="213"/>
+      <x:c r="C22" s="213"/>
+      <x:c r="D22" s="213"/>
+      <x:c r="E22" s="213"/>
+      <x:c r="F22" s="213"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="213"/>
+      <x:c r="B23" s="213"/>
+      <x:c r="C23" s="213"/>
+      <x:c r="D23" s="213"/>
+      <x:c r="E23" s="213"/>
+      <x:c r="F23" s="213"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="213"/>
+      <x:c r="B24" s="213"/>
+      <x:c r="C24" s="213"/>
+      <x:c r="D24" s="213"/>
+      <x:c r="E24" s="213"/>
+      <x:c r="F24" s="213"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="213"/>
+      <x:c r="B25" s="213"/>
+      <x:c r="C25" s="213"/>
+      <x:c r="D25" s="213"/>
+      <x:c r="E25" s="213"/>
+      <x:c r="F25" s="213"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="213"/>
+      <x:c r="B26" s="213"/>
+      <x:c r="C26" s="213"/>
+      <x:c r="D26" s="213"/>
+      <x:c r="E26" s="213"/>
+      <x:c r="F26" s="213"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="213"/>
+      <x:c r="B27" s="213"/>
+      <x:c r="C27" s="213"/>
+      <x:c r="D27" s="213"/>
+      <x:c r="E27" s="213"/>
+      <x:c r="F27" s="213"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="213"/>
+      <x:c r="B28" s="213"/>
+      <x:c r="C28" s="213"/>
+      <x:c r="D28" s="213"/>
+      <x:c r="E28" s="213"/>
+      <x:c r="F28" s="213"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="213"/>
+      <x:c r="B29" s="213"/>
+      <x:c r="C29" s="213"/>
+      <x:c r="D29" s="213"/>
+      <x:c r="E29" s="213"/>
+      <x:c r="F29" s="213"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="213"/>
+      <x:c r="B30" s="213"/>
+      <x:c r="C30" s="213"/>
+      <x:c r="D30" s="213"/>
+      <x:c r="E30" s="213"/>
+      <x:c r="F30" s="213"/>
+    </x:row>
+    <x:row r="31" ht="30" customHeight="1">
+      <x:c r="A31" s="218" t="str">
+        <x:v>Break-even — Find the minimum event attendance</x:v>
+      </x:c>
+      <x:c r="B31" s="218"/>
+      <x:c r="C31" s="218"/>
+      <x:c r="D31" s="218"/>
+      <x:c r="E31" s="218"/>
+      <x:c r="F31" s="218"/>
+    </x:row>
+    <x:row r="32" ht="32" customHeight="1">
+      <x:c r="A32" s="220" t="str">
+        <x:v>Anchor &amp; Oak plans a community dinner. Venue, permits, and base staffing total $4,250. Tickets sell for $58 per guest; food and service cost $32 per guest. How many whole guests are needed to cover the event costs?</x:v>
+      </x:c>
+      <x:c r="B32" s="220"/>
+      <x:c r="C32" s="220"/>
+      <x:c r="D32" s="220"/>
+      <x:c r="E32" s="220"/>
+      <x:c r="F32" s="220"/>
+    </x:row>
+    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="A33" s="220"/>
+      <x:c r="B33" s="220"/>
+      <x:c r="C33" s="220"/>
+      <x:c r="D33" s="220"/>
+      <x:c r="E33" s="220"/>
+      <x:c r="F33" s="220"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="213"/>
+      <x:c r="B34" s="213"/>
+      <x:c r="C34" s="213"/>
+      <x:c r="D34" s="213"/>
+      <x:c r="E34" s="213"/>
+      <x:c r="F34" s="213"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="213"/>
+      <x:c r="B35" s="213"/>
+      <x:c r="C35" s="213"/>
+      <x:c r="D35" s="213"/>
+      <x:c r="E35" s="213"/>
+      <x:c r="F35" s="213"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="213"/>
+      <x:c r="B36" s="213"/>
+      <x:c r="C36" s="213"/>
+      <x:c r="D36" s="213"/>
+      <x:c r="E36" s="213"/>
+      <x:c r="F36" s="213"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="213"/>
+      <x:c r="B37" s="213"/>
+      <x:c r="C37" s="213"/>
+      <x:c r="D37" s="213"/>
+      <x:c r="E37" s="213"/>
+      <x:c r="F37" s="213"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="213"/>
+      <x:c r="B38" s="213"/>
+      <x:c r="C38" s="213"/>
+      <x:c r="D38" s="213"/>
+      <x:c r="E38" s="213"/>
+      <x:c r="F38" s="213"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="213"/>
+      <x:c r="B39" s="213"/>
+      <x:c r="C39" s="213"/>
+      <x:c r="D39" s="213"/>
+      <x:c r="E39" s="213"/>
+      <x:c r="F39" s="213"/>
+    </x:row>
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="213"/>
+      <x:c r="B40" s="213"/>
+      <x:c r="C40" s="213"/>
+      <x:c r="D40" s="213"/>
+      <x:c r="E40" s="213"/>
+      <x:c r="F40" s="213"/>
+    </x:row>
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41" s="213"/>
+      <x:c r="B41" s="213"/>
+      <x:c r="C41" s="213"/>
+      <x:c r="D41" s="213"/>
+      <x:c r="E41" s="213"/>
+      <x:c r="F41" s="213"/>
+    </x:row>
+    <x:row r="42" ht="24" customHeight="1">
+      <x:c r="A42" s="213"/>
+      <x:c r="B42" s="213"/>
+      <x:c r="C42" s="213"/>
+      <x:c r="D42" s="213"/>
+      <x:c r="E42" s="213"/>
+      <x:c r="F42" s="213"/>
+    </x:row>
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="213"/>
+      <x:c r="B43" s="213"/>
+      <x:c r="C43" s="213"/>
+      <x:c r="D43" s="213"/>
+      <x:c r="E43" s="213"/>
+      <x:c r="F43" s="213"/>
+    </x:row>
+    <x:row r="44" ht="24" customHeight="1">
+      <x:c r="A44" s="213"/>
+      <x:c r="B44" s="213"/>
+      <x:c r="C44" s="213"/>
+      <x:c r="D44" s="213"/>
+      <x:c r="E44" s="213"/>
+      <x:c r="F44" s="213"/>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="213"/>
+      <x:c r="B45" s="213"/>
+      <x:c r="C45" s="213"/>
+      <x:c r="D45" s="213"/>
+      <x:c r="E45" s="213"/>
+      <x:c r="F45" s="213"/>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="213"/>
+      <x:c r="B46" s="213"/>
+      <x:c r="C46" s="213"/>
+      <x:c r="D46" s="213"/>
+      <x:c r="E46" s="213"/>
+      <x:c r="F46" s="213"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A3:F3"/>
-    <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A4:F4"/>
+    <x:mergeCell ref="A5:F6"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A19:F20"/>
+    <x:mergeCell ref="A31:F31"/>
+    <x:mergeCell ref="A32:F33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
